--- a/assets/translations/Czech.Czechia.cz-CZ.xlsx
+++ b/assets/translations/Czech.Czechia.cz-CZ.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bendova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4CA7B9-DC64-3A4B-A133-17A1A3FAA642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="9150" windowHeight="8595" activeTab="1"/>
+    <workbookView xWindow="5020" yWindow="4860" windowWidth="23960" windowHeight="16240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
     <sheet name="Statements" sheetId="1" r:id="rId2"/>
     <sheet name="Key messages" sheetId="4" r:id="rId3"/>
+    <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="210">
   <si>
     <t>Number</t>
   </si>
@@ -663,12 +665,39 @@
   <si>
     <t>Kontextové informace</t>
   </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>Consensus statements (Czech)</t>
+  </si>
+  <si>
+    <t>Seznam literatury</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>Klíčová sdělení</t>
+  </si>
+  <si>
+    <t>Artemide</t>
+  </si>
+  <si>
+    <t>Číslo</t>
+  </si>
+  <si>
+    <t>Kapitola</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -782,6 +811,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -967,11 +1018,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1052,10 +1104,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hypertextový odkaz" xfId="1" builtinId="8"/>
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{7AAC50E4-FBC9-EC48-B5C8-5D76F589FF86}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1371,19 +1429,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
     <col min="2" max="3" width="21.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.875" style="2"/>
+    <col min="4" max="4" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
@@ -1404,7 +1462,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="25" customFormat="1" ht="15.75">
+    <row r="2" spans="1:7" s="25" customFormat="1">
       <c r="A2" s="25" t="s">
         <v>150</v>
       </c>
@@ -1414,9 +1472,12 @@
       <c r="D2" s="11" t="s">
         <v>147</v>
       </c>
+      <c r="E2" s="25" t="s">
+        <v>207</v>
+      </c>
       <c r="F2" s="11"/>
     </row>
-    <row r="3" spans="1:7" s="25" customFormat="1" ht="15.75">
+    <row r="3" spans="1:7" s="25" customFormat="1">
       <c r="A3" s="25" t="s">
         <v>188</v>
       </c>
@@ -1437,14 +1498,14 @@
       </c>
     </row>
     <row r="4" spans="1:7" s="25" customFormat="1"/>
-    <row r="5" spans="1:7" s="25" customFormat="1" ht="15.75">
+    <row r="5" spans="1:7" s="25" customFormat="1">
       <c r="D5" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
@@ -1452,47 +1513,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="22.375" customWidth="1"/>
-    <col min="2" max="2" width="25.125" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="8" width="42.375" customWidth="1"/>
-    <col min="9" max="9" width="42.375" style="18" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="9" width="42.33203125" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>69</v>
+      <c r="B1" t="s">
+        <v>209</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="22" customFormat="1" ht="75">
+    <row r="2" spans="1:10" s="22" customFormat="1" ht="85">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -1502,26 +1566,29 @@
       <c r="C2" s="26">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="26">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="H2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="75">
+    <row r="3" spans="1:10" ht="85">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -1531,26 +1598,29 @@
       <c r="C3" s="26">
         <v>2</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="26">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="H3" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="94.5">
+    <row r="4" spans="1:10" ht="119">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -1560,26 +1630,29 @@
       <c r="C4" s="26">
         <v>3</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="26">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="H4" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="90">
+    <row r="5" spans="1:10" ht="102">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -1589,26 +1662,29 @@
       <c r="C5" s="7">
         <v>4</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="F5" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="H5" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="J5" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="94.5">
+    <row r="6" spans="1:10" ht="119">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -1618,26 +1694,29 @@
       <c r="C6" s="7">
         <v>5</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7">
+        <v>5</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="F6" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="J6" s="13" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="69">
+    <row r="7" spans="1:10" ht="68">
       <c r="A7" t="s">
         <v>90</v>
       </c>
@@ -1647,26 +1726,29 @@
       <c r="C7" s="7">
         <v>6</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="F7" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="H7" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="78">
+    <row r="8" spans="1:10" ht="87">
       <c r="A8" t="s">
         <v>91</v>
       </c>
@@ -1676,26 +1758,29 @@
       <c r="C8" s="7">
         <v>7</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7">
+        <v>7</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="H8" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="J8" s="13" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="78.75">
+    <row r="9" spans="1:10" ht="85">
       <c r="A9" t="s">
         <v>91</v>
       </c>
@@ -1705,26 +1790,29 @@
       <c r="C9" s="7">
         <v>8</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7">
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="F9" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="H9" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34.5">
+    <row r="10" spans="1:10" ht="38">
       <c r="A10" t="s">
         <v>91</v>
       </c>
@@ -1734,26 +1822,29 @@
       <c r="C10" s="7">
         <v>9</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7">
+        <v>9</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="F10" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="G10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="H10" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="I10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="J10" s="13" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="47.25">
+    <row r="11" spans="1:10" ht="68">
       <c r="A11" t="s">
         <v>92</v>
       </c>
@@ -1763,26 +1854,29 @@
       <c r="C11" s="7">
         <v>10</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="F11" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="G11" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="H11" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="I11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="J11" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="90">
+    <row r="12" spans="1:10" ht="102">
       <c r="A12" t="s">
         <v>92</v>
       </c>
@@ -1792,26 +1886,29 @@
       <c r="C12" s="7">
         <v>11</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7">
+        <v>11</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="H12" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="J12" s="13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="51.75">
+    <row r="13" spans="1:10" ht="57">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1821,26 +1918,29 @@
       <c r="C13" s="7">
         <v>12</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7">
+        <v>12</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="F13" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="H13" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="51.75">
+    <row r="14" spans="1:10" ht="57">
       <c r="A14" t="s">
         <v>92</v>
       </c>
@@ -1850,26 +1950,29 @@
       <c r="C14" s="7">
         <v>13</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7">
+        <v>13</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="F14" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="G14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="H14" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="J14" s="13" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="69">
+    <row r="15" spans="1:10" ht="85">
       <c r="A15" t="s">
         <v>92</v>
       </c>
@@ -1879,26 +1982,29 @@
       <c r="C15" s="7">
         <v>14</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7">
+        <v>14</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="F15" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="H15" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="13" t="s">
+      <c r="J15" s="13" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="60">
+    <row r="16" spans="1:10" ht="68">
       <c r="A16" t="s">
         <v>92</v>
       </c>
@@ -1908,26 +2014,29 @@
       <c r="C16" s="7">
         <v>15</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7">
+        <v>15</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="F16" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="H16" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="J16" s="13" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="60">
+    <row r="17" spans="1:10" ht="68">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -1937,26 +2046,29 @@
       <c r="C17" s="7">
         <v>16</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7">
+        <v>16</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="H17" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="J17" s="13" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="47.25">
+    <row r="18" spans="1:10" ht="51">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1966,26 +2078,29 @@
       <c r="C18" s="7">
         <v>17</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7">
+        <v>17</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="F18" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="H18" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I18" s="13" t="s">
+      <c r="J18" s="13" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="63">
+    <row r="19" spans="1:10" ht="68">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -1995,26 +2110,29 @@
       <c r="C19" s="7">
         <v>18</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="F19" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="H19" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="J19" s="13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="60">
+    <row r="20" spans="1:10" ht="68">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -2024,26 +2142,29 @@
       <c r="C20" s="7">
         <v>19</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7">
+        <v>19</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="F20" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="15" t="s">
+      <c r="H20" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="13" t="s">
+      <c r="J20" s="13" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="86.25">
+    <row r="21" spans="1:10" ht="95">
       <c r="A21" t="s">
         <v>92</v>
       </c>
@@ -2053,26 +2174,29 @@
       <c r="C21" s="7">
         <v>20</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7">
+        <v>20</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="F21" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="G21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="H21" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="I21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="J21" s="13" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="60">
+    <row r="22" spans="1:10" ht="68">
       <c r="A22" t="s">
         <v>93</v>
       </c>
@@ -2082,26 +2206,29 @@
       <c r="C22" s="7">
         <v>21</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7">
+        <v>21</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="F22" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="G22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="H22" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="13" t="s">
+      <c r="J22" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="60">
+    <row r="23" spans="1:10" ht="68">
       <c r="A23" t="s">
         <v>93</v>
       </c>
@@ -2111,26 +2238,29 @@
       <c r="C23" s="7">
         <v>22</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7">
+        <v>22</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="F23" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="H23" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="J23" s="13" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="45">
+    <row r="24" spans="1:10" ht="51">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -2140,26 +2270,29 @@
       <c r="C24" s="7">
         <v>23</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7">
+        <v>23</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="F24" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="H24" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="J24" s="13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="45">
+    <row r="25" spans="1:10" ht="51">
       <c r="A25" t="s">
         <v>94</v>
       </c>
@@ -2169,26 +2302,29 @@
       <c r="C25" s="7">
         <v>24</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7">
+        <v>24</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="G25" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="H25" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="J25" s="13" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="90">
+    <row r="26" spans="1:10" ht="102">
       <c r="A26" t="s">
         <v>94</v>
       </c>
@@ -2198,26 +2334,29 @@
       <c r="C26" s="7">
         <v>25</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7">
+        <v>25</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="F26" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="G26" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="H26" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="I26" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I26" s="13" t="s">
+      <c r="J26" s="13" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="90.75" thickBot="1">
+    <row r="27" spans="1:10" ht="120" thickBot="1">
       <c r="A27" t="s">
         <v>94</v>
       </c>
@@ -2227,22 +2366,25 @@
       <c r="C27" s="9">
         <v>26</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9">
+        <v>26</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="F27" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="G27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="H27" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="I27" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I27" s="24" t="s">
+      <c r="J27" s="24" t="s">
         <v>187</v>
       </c>
     </row>
@@ -2254,15 +2396,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="19.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="29" t="s">
         <v>95</v>
       </c>
@@ -2270,44 +2412,91 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="114.95" customHeight="1">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:2" ht="21">
+      <c r="A2" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="115" customHeight="1">
+      <c r="A3" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B3" s="28" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58.5">
-      <c r="A3" s="29" t="s">
+    <row r="4" spans="1:2" ht="63">
+      <c r="A4" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B4" s="28" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="78">
-      <c r="A4" s="29" t="s">
+    <row r="5" spans="1:2" ht="84">
+      <c r="A5" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B5" s="28" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="78">
-      <c r="A5" s="29" t="s">
+    <row r="6" spans="1:2" ht="84">
+      <c r="A6" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B6" s="28" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="78.75">
-      <c r="A6" s="29" t="s">
+    <row r="7" spans="1:2" ht="85">
+      <c r="A7" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B7" s="28" t="s">
         <v>149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E93D1B-7511-BD41-913C-84ADA212FF46}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="30" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="30" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
